--- a/ParagonFakeDataForMacroTesting.xlsx
+++ b/ParagonFakeDataForMacroTesting.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshua/Documents/Paragon Workflow/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E755D007-C549-7140-8425-C4A56D917CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{311C7DD5-321C-2745-8450-BD4E9D2ED50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="35" r:id="rId1"/>
     <sheet name="unmapped-corp" sheetId="36" r:id="rId2"/>
-    <sheet name="s1" sheetId="37" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="38" r:id="rId4"/>
-    <sheet name="Sheet6" sheetId="39" r:id="rId5"/>
-    <sheet name="OUTERSKEY" sheetId="7" r:id="rId6"/>
+    <sheet name="FilteredData" sheetId="51" r:id="rId3"/>
+    <sheet name="s1" sheetId="37" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="38" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="39" r:id="rId6"/>
+    <sheet name="OUTERSKEY" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="647">
   <si>
     <t>JOSH</t>
   </si>
@@ -1865,13 +1866,130 @@
   </si>
   <si>
     <t>ENV0517 09/17</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>capb or save</t>
+  </si>
+  <si>
+    <t>misc1280</t>
+  </si>
+  <si>
+    <t>bank200feb</t>
+  </si>
+  <si>
+    <t>misc1640</t>
+  </si>
+  <si>
+    <t>misc1638</t>
+  </si>
+  <si>
+    <t>misc1860</t>
+  </si>
+  <si>
+    <t>misc1880</t>
+  </si>
+  <si>
+    <t>misc1881</t>
+  </si>
+  <si>
+    <t>Santander Banking</t>
+  </si>
+  <si>
+    <t>AMFA1</t>
+  </si>
+  <si>
+    <t>wdewef</t>
+  </si>
+  <si>
+    <t>SFEERF</t>
+  </si>
+  <si>
+    <t>REF</t>
+  </si>
+  <si>
+    <t>SEF</t>
+  </si>
+  <si>
+    <t>AMFA2</t>
+  </si>
+  <si>
+    <t>AMFA3</t>
+  </si>
+  <si>
+    <t>AMFA4</t>
+  </si>
+  <si>
+    <t>AMFA5</t>
+  </si>
+  <si>
+    <t>OUTER</t>
+  </si>
+  <si>
+    <t>Color Key</t>
+  </si>
+  <si>
+    <t>Remakes</t>
+  </si>
+  <si>
+    <t>C4 Outers</t>
+  </si>
+  <si>
+    <t>Work Orders Of Jobs With Inserts</t>
+  </si>
+  <si>
+    <t>Work Orders Of Jobs With Outers We Should Order (0 Inserts)</t>
+  </si>
+  <si>
+    <t>New Entries</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>STOCK_LOCATION</t>
+  </si>
+  <si>
+    <t>MAIL PROVIDER</t>
+  </si>
+  <si>
+    <t>S1376</t>
+  </si>
+  <si>
+    <t>S19Y2</t>
+  </si>
+  <si>
+    <t>S19Y3</t>
+  </si>
+  <si>
+    <t>S19Y5</t>
+  </si>
+  <si>
+    <t>S19Y6</t>
+  </si>
+  <si>
+    <t>S19Y7</t>
+  </si>
+  <si>
+    <t>SCJ12</t>
+  </si>
+  <si>
+    <t>S7043</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>S2134</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1972,8 +2090,23 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2040,6 +2173,48 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE8FCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFAB60"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8C8C8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4F9E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3333"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -2085,7 +2260,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -2151,6 +2326,47 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4737,9 +4953,1284 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{110002EF-FF41-5547-99A1-1D1847926380}">
+  <dimension ref="A1:I63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" style="41" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="39" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
+    <col min="7" max="7" width="3.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" style="41" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="44" t="s">
+        <v>636</v>
+      </c>
+      <c r="I1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="47">
+        <v>30021</v>
+      </c>
+      <c r="D2" s="45">
+        <v>68</v>
+      </c>
+      <c r="E2" s="45">
+        <v>44</v>
+      </c>
+      <c r="F2" s="45"/>
+      <c r="G2" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="47">
+        <v>30022</v>
+      </c>
+      <c r="D3" s="45">
+        <v>68</v>
+      </c>
+      <c r="E3" s="45">
+        <v>44</v>
+      </c>
+      <c r="F3" s="45"/>
+      <c r="G3" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="47">
+        <v>30025</v>
+      </c>
+      <c r="D4" s="45">
+        <v>68</v>
+      </c>
+      <c r="E4" s="45">
+        <v>44</v>
+      </c>
+      <c r="F4" s="45"/>
+      <c r="G4" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="46">
+        <v>34022</v>
+      </c>
+      <c r="D5" s="45">
+        <v>5343</v>
+      </c>
+      <c r="E5" s="45">
+        <v>0</v>
+      </c>
+      <c r="F5" s="45"/>
+      <c r="G5" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="43">
+        <v>34023</v>
+      </c>
+      <c r="D6" s="45">
+        <v>324</v>
+      </c>
+      <c r="E6" s="45">
+        <v>0</v>
+      </c>
+      <c r="F6" s="45"/>
+      <c r="G6" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="43">
+        <v>34024</v>
+      </c>
+      <c r="D7" s="45">
+        <v>5679</v>
+      </c>
+      <c r="E7" s="45">
+        <v>0</v>
+      </c>
+      <c r="F7" s="45"/>
+      <c r="G7" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="49">
+        <v>34025</v>
+      </c>
+      <c r="D8" s="50">
+        <v>32790</v>
+      </c>
+      <c r="E8" s="50">
+        <v>0</v>
+      </c>
+      <c r="F8" s="50">
+        <v>44</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="52"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="43">
+        <v>34026</v>
+      </c>
+      <c r="D9" s="45">
+        <v>68</v>
+      </c>
+      <c r="E9" s="45">
+        <v>0</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="65" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="43">
+        <v>34027</v>
+      </c>
+      <c r="D10" s="45">
+        <v>190</v>
+      </c>
+      <c r="E10" s="45">
+        <v>0</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="43">
+        <v>34028</v>
+      </c>
+      <c r="D11" s="45">
+        <v>25400</v>
+      </c>
+      <c r="E11" s="45">
+        <v>0</v>
+      </c>
+      <c r="F11" s="45"/>
+      <c r="G11" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>618</v>
+      </c>
+      <c r="C12" s="47">
+        <v>45621</v>
+      </c>
+      <c r="D12" s="45">
+        <v>300</v>
+      </c>
+      <c r="E12" s="45">
+        <v>6</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>623</v>
+      </c>
+      <c r="C13" s="47">
+        <v>45622</v>
+      </c>
+      <c r="D13" s="45">
+        <v>300</v>
+      </c>
+      <c r="E13" s="45">
+        <v>6</v>
+      </c>
+      <c r="F13" s="45"/>
+      <c r="G13" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>624</v>
+      </c>
+      <c r="C14" s="47">
+        <v>45623</v>
+      </c>
+      <c r="D14" s="45">
+        <v>300</v>
+      </c>
+      <c r="E14" s="45">
+        <v>6</v>
+      </c>
+      <c r="F14" s="45"/>
+      <c r="G14" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>625</v>
+      </c>
+      <c r="C15" s="47">
+        <v>45624</v>
+      </c>
+      <c r="D15" s="45">
+        <v>300</v>
+      </c>
+      <c r="E15" s="45">
+        <v>6</v>
+      </c>
+      <c r="F15" s="45"/>
+      <c r="G15" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="C16" s="47">
+        <v>45625</v>
+      </c>
+      <c r="D16" s="45">
+        <v>300</v>
+      </c>
+      <c r="E16" s="45">
+        <v>6</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>637</v>
+      </c>
+      <c r="C17" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D17" s="45">
+        <v>2</v>
+      </c>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="C18" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D18" s="45">
+        <v>1</v>
+      </c>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>639</v>
+      </c>
+      <c r="C19" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D19" s="45">
+        <v>1</v>
+      </c>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>646</v>
+      </c>
+      <c r="C20" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D20" s="45">
+        <v>1</v>
+      </c>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="C21" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D21" s="45">
+        <v>1</v>
+      </c>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>641</v>
+      </c>
+      <c r="C22" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D22" s="45">
+        <v>1</v>
+      </c>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>642</v>
+      </c>
+      <c r="C23" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D23" s="45">
+        <v>1</v>
+      </c>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="C24" s="43">
+        <v>45625</v>
+      </c>
+      <c r="D24" s="45">
+        <v>500</v>
+      </c>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="51" t="s">
+        <v>617</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>644</v>
+      </c>
+      <c r="C25" s="49">
+        <v>45625</v>
+      </c>
+      <c r="D25" s="50">
+        <v>1800</v>
+      </c>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50" t="s">
+        <v>645</v>
+      </c>
+      <c r="G25" s="48" t="s">
+        <v>645</v>
+      </c>
+      <c r="H25" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="52" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="43">
+        <v>80023</v>
+      </c>
+      <c r="D26" s="45">
+        <v>4500</v>
+      </c>
+      <c r="E26" s="45">
+        <v>0</v>
+      </c>
+      <c r="F26" s="45"/>
+      <c r="G26" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="40"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="47">
+        <v>80024</v>
+      </c>
+      <c r="D27" s="45">
+        <v>8000</v>
+      </c>
+      <c r="E27" s="45">
+        <v>55</v>
+      </c>
+      <c r="F27" s="45"/>
+      <c r="G27" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="40"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="47">
+        <v>80025</v>
+      </c>
+      <c r="D28" s="45">
+        <v>9500</v>
+      </c>
+      <c r="E28" s="45">
+        <v>44</v>
+      </c>
+      <c r="F28" s="45"/>
+      <c r="G28" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="40"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="43">
+        <v>80026</v>
+      </c>
+      <c r="D29" s="45">
+        <v>62</v>
+      </c>
+      <c r="E29" s="45">
+        <v>4</v>
+      </c>
+      <c r="F29" s="45"/>
+      <c r="G29" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="40"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="43">
+        <v>80027</v>
+      </c>
+      <c r="D30" s="45">
+        <v>69</v>
+      </c>
+      <c r="E30" s="45">
+        <v>4</v>
+      </c>
+      <c r="F30" s="45"/>
+      <c r="G30" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="49">
+        <v>99901</v>
+      </c>
+      <c r="D31" s="50">
+        <v>500</v>
+      </c>
+      <c r="E31" s="50">
+        <v>4</v>
+      </c>
+      <c r="F31" s="50">
+        <v>6</v>
+      </c>
+      <c r="G31" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="52"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="43">
+        <v>99904</v>
+      </c>
+      <c r="D32" s="45">
+        <v>95</v>
+      </c>
+      <c r="E32" s="45">
+        <v>0</v>
+      </c>
+      <c r="F32" s="45"/>
+      <c r="G32" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="43">
+        <v>99905</v>
+      </c>
+      <c r="D33" s="45">
+        <v>2000</v>
+      </c>
+      <c r="E33" s="45">
+        <v>0</v>
+      </c>
+      <c r="F33" s="45"/>
+      <c r="G33" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="47">
+        <v>99908</v>
+      </c>
+      <c r="D34" s="45">
+        <v>10090</v>
+      </c>
+      <c r="E34" s="45">
+        <v>5</v>
+      </c>
+      <c r="F34" s="45"/>
+      <c r="G34" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="47">
+        <v>99911</v>
+      </c>
+      <c r="D35" s="45">
+        <v>42090</v>
+      </c>
+      <c r="E35" s="45">
+        <v>500</v>
+      </c>
+      <c r="F35" s="45"/>
+      <c r="G35" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="47">
+        <v>99921</v>
+      </c>
+      <c r="D36" s="45">
+        <v>50500</v>
+      </c>
+      <c r="E36" s="45">
+        <v>55</v>
+      </c>
+      <c r="F36" s="45"/>
+      <c r="G36" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H36" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="47">
+        <v>99976</v>
+      </c>
+      <c r="D37" s="45">
+        <v>68</v>
+      </c>
+      <c r="E37" s="45">
+        <v>44</v>
+      </c>
+      <c r="F37" s="45"/>
+      <c r="G37" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H37" s="44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="49">
+        <v>99983</v>
+      </c>
+      <c r="D38" s="50">
+        <v>123</v>
+      </c>
+      <c r="E38" s="50">
+        <v>123</v>
+      </c>
+      <c r="F38" s="50">
+        <v>7</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="52"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" s="45">
+        <v>798</v>
+      </c>
+      <c r="E39" s="45">
+        <v>0</v>
+      </c>
+      <c r="F39" s="45"/>
+      <c r="G39" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="H39" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="53" t="s">
+        <v>628</v>
+      </c>
+      <c r="B42" s="53"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="54" t="s">
+        <v>629</v>
+      </c>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="55" t="s">
+        <v>630</v>
+      </c>
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" s="56" t="s">
+        <v>631</v>
+      </c>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="57" t="s">
+        <v>632</v>
+      </c>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="58" t="s">
+        <v>633</v>
+      </c>
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="59" t="s">
+        <v>627</v>
+      </c>
+      <c r="B53" s="59"/>
+      <c r="C53" s="60" t="s">
+        <v>634</v>
+      </c>
+      <c r="D53" s="61" t="s">
+        <v>635</v>
+      </c>
+      <c r="E53" s="61"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="62" t="s">
+        <v>397</v>
+      </c>
+      <c r="B54" s="62"/>
+      <c r="C54" s="63">
+        <v>2</v>
+      </c>
+      <c r="D54" s="64"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="64"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="62"/>
+      <c r="C55" s="63">
+        <v>5343</v>
+      </c>
+      <c r="D55" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" s="62"/>
+      <c r="C56" s="63">
+        <v>204</v>
+      </c>
+      <c r="D56" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="62" t="s">
+        <v>409</v>
+      </c>
+      <c r="B57" s="62"/>
+      <c r="C57" s="63">
+        <v>5</v>
+      </c>
+      <c r="D57" s="64" t="s">
+        <v>610</v>
+      </c>
+      <c r="E57" s="64"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="62" t="s">
+        <v>411</v>
+      </c>
+      <c r="B58" s="62"/>
+      <c r="C58" s="63">
+        <v>1</v>
+      </c>
+      <c r="D58" s="64" t="s">
+        <v>612</v>
+      </c>
+      <c r="E58" s="64"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="64"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="62" t="s">
+        <v>427</v>
+      </c>
+      <c r="B59" s="62"/>
+      <c r="C59" s="63">
+        <v>500</v>
+      </c>
+      <c r="D59" s="64" t="s">
+        <v>614</v>
+      </c>
+      <c r="E59" s="64"/>
+      <c r="F59" s="64"/>
+      <c r="G59" s="64"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="B60" s="62"/>
+      <c r="C60" s="63">
+        <v>1500</v>
+      </c>
+      <c r="D60" s="64" t="s">
+        <v>608</v>
+      </c>
+      <c r="E60" s="64"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="64"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="62" t="s">
+        <v>399</v>
+      </c>
+      <c r="B61" s="62"/>
+      <c r="C61" s="63">
+        <v>1800</v>
+      </c>
+      <c r="D61" s="64"/>
+      <c r="E61" s="64"/>
+      <c r="F61" s="64"/>
+      <c r="G61" s="64"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="62"/>
+      <c r="C62" s="63">
+        <v>798</v>
+      </c>
+      <c r="D62" s="64"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="64"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="62"/>
+      <c r="C63" s="63">
+        <v>52180</v>
+      </c>
+      <c r="D63" s="64"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="64"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A54:D63">
+    <sortCondition ref="A1:A1048576"/>
+  </sortState>
+  <mergeCells count="28">
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="D59:G59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="D61:G61"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="D58:G58"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:F47"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter>
+    <oddHeader>&amp;R14:42 - 26/05/2025&amp;LPage: &amp;P</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A47EC9-6FF9-C94A-93F5-603B3A771B7A}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="16" max="17" width="28.33203125" bestFit="1" customWidth="1"/>
@@ -6083,13 +7574,732 @@
         <v>3</v>
       </c>
     </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>617</v>
+      </c>
+      <c r="B26" t="s">
+        <v>618</v>
+      </c>
+      <c r="C26" t="s">
+        <v>619</v>
+      </c>
+      <c r="D26">
+        <v>45621</v>
+      </c>
+      <c r="E26">
+        <v>23</v>
+      </c>
+      <c r="F26">
+        <v>23</v>
+      </c>
+      <c r="G26">
+        <v>300</v>
+      </c>
+      <c r="H26">
+        <v>6</v>
+      </c>
+      <c r="J26" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>4</v>
+      </c>
+      <c r="L26" t="s">
+        <v>620</v>
+      </c>
+      <c r="M26" t="s">
+        <v>621</v>
+      </c>
+      <c r="N26" t="s">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>622</v>
+      </c>
+      <c r="P26" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>617</v>
+      </c>
+      <c r="B27" t="s">
+        <v>623</v>
+      </c>
+      <c r="C27" t="s">
+        <v>619</v>
+      </c>
+      <c r="D27">
+        <v>45622</v>
+      </c>
+      <c r="E27">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>23</v>
+      </c>
+      <c r="G27">
+        <v>300</v>
+      </c>
+      <c r="H27">
+        <v>6</v>
+      </c>
+      <c r="J27" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" t="s">
+        <v>620</v>
+      </c>
+      <c r="M27" t="s">
+        <v>621</v>
+      </c>
+      <c r="N27" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>622</v>
+      </c>
+      <c r="P27" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>617</v>
+      </c>
+      <c r="B28" t="s">
+        <v>624</v>
+      </c>
+      <c r="C28" t="s">
+        <v>619</v>
+      </c>
+      <c r="D28">
+        <v>45623</v>
+      </c>
+      <c r="E28">
+        <v>23</v>
+      </c>
+      <c r="F28">
+        <v>23</v>
+      </c>
+      <c r="G28">
+        <v>300</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="J28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K28" t="s">
+        <v>4</v>
+      </c>
+      <c r="L28" t="s">
+        <v>620</v>
+      </c>
+      <c r="M28" t="s">
+        <v>621</v>
+      </c>
+      <c r="N28" t="s">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>622</v>
+      </c>
+      <c r="P28" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>3</v>
+      </c>
+      <c r="R28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>617</v>
+      </c>
+      <c r="B29" t="s">
+        <v>625</v>
+      </c>
+      <c r="C29" t="s">
+        <v>619</v>
+      </c>
+      <c r="D29">
+        <v>45624</v>
+      </c>
+      <c r="E29">
+        <v>23</v>
+      </c>
+      <c r="F29">
+        <v>23</v>
+      </c>
+      <c r="G29">
+        <v>300</v>
+      </c>
+      <c r="H29">
+        <v>6</v>
+      </c>
+      <c r="J29" t="s">
+        <v>4</v>
+      </c>
+      <c r="K29" t="s">
+        <v>4</v>
+      </c>
+      <c r="L29" t="s">
+        <v>620</v>
+      </c>
+      <c r="M29" t="s">
+        <v>621</v>
+      </c>
+      <c r="N29" t="s">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>622</v>
+      </c>
+      <c r="P29" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>617</v>
+      </c>
+      <c r="B30" t="s">
+        <v>626</v>
+      </c>
+      <c r="C30" t="s">
+        <v>619</v>
+      </c>
+      <c r="D30">
+        <v>45625</v>
+      </c>
+      <c r="E30">
+        <v>23</v>
+      </c>
+      <c r="F30">
+        <v>23</v>
+      </c>
+      <c r="G30">
+        <v>300</v>
+      </c>
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="J30" t="s">
+        <v>4</v>
+      </c>
+      <c r="K30" t="s">
+        <v>4</v>
+      </c>
+      <c r="L30" t="s">
+        <v>620</v>
+      </c>
+      <c r="M30" t="s">
+        <v>621</v>
+      </c>
+      <c r="N30" t="s">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>622</v>
+      </c>
+      <c r="P30" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>3</v>
+      </c>
+      <c r="R30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>617</v>
+      </c>
+      <c r="B31" t="s">
+        <v>637</v>
+      </c>
+      <c r="C31" t="s">
+        <v>619</v>
+      </c>
+      <c r="D31">
+        <v>45625</v>
+      </c>
+      <c r="E31">
+        <v>23</v>
+      </c>
+      <c r="F31">
+        <v>23</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="J31" t="s">
+        <v>4</v>
+      </c>
+      <c r="K31" t="s">
+        <v>4</v>
+      </c>
+      <c r="L31" t="s">
+        <v>620</v>
+      </c>
+      <c r="M31" t="s">
+        <v>621</v>
+      </c>
+      <c r="N31" t="s">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>622</v>
+      </c>
+      <c r="P31" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>3</v>
+      </c>
+      <c r="R31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>617</v>
+      </c>
+      <c r="B32" t="s">
+        <v>638</v>
+      </c>
+      <c r="C32" t="s">
+        <v>619</v>
+      </c>
+      <c r="D32">
+        <v>45625</v>
+      </c>
+      <c r="E32">
+        <v>23</v>
+      </c>
+      <c r="F32">
+        <v>23</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" t="s">
+        <v>620</v>
+      </c>
+      <c r="M32" t="s">
+        <v>621</v>
+      </c>
+      <c r="N32" t="s">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>622</v>
+      </c>
+      <c r="P32" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>617</v>
+      </c>
+      <c r="B33" t="s">
+        <v>639</v>
+      </c>
+      <c r="C33" t="s">
+        <v>619</v>
+      </c>
+      <c r="D33">
+        <v>45625</v>
+      </c>
+      <c r="E33">
+        <v>23</v>
+      </c>
+      <c r="F33">
+        <v>23</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" t="s">
+        <v>4</v>
+      </c>
+      <c r="L33" t="s">
+        <v>620</v>
+      </c>
+      <c r="M33" t="s">
+        <v>621</v>
+      </c>
+      <c r="N33" t="s">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>622</v>
+      </c>
+      <c r="P33" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>617</v>
+      </c>
+      <c r="B34" t="s">
+        <v>646</v>
+      </c>
+      <c r="C34" t="s">
+        <v>619</v>
+      </c>
+      <c r="D34">
+        <v>45625</v>
+      </c>
+      <c r="E34">
+        <v>23</v>
+      </c>
+      <c r="F34">
+        <v>23</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="J34" t="s">
+        <v>4</v>
+      </c>
+      <c r="K34" t="s">
+        <v>4</v>
+      </c>
+      <c r="L34" t="s">
+        <v>620</v>
+      </c>
+      <c r="M34" t="s">
+        <v>621</v>
+      </c>
+      <c r="N34" t="s">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>622</v>
+      </c>
+      <c r="P34" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>4</v>
+      </c>
+      <c r="R34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>617</v>
+      </c>
+      <c r="B35" t="s">
+        <v>640</v>
+      </c>
+      <c r="C35" t="s">
+        <v>619</v>
+      </c>
+      <c r="D35">
+        <v>45625</v>
+      </c>
+      <c r="E35">
+        <v>23</v>
+      </c>
+      <c r="F35">
+        <v>23</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="J35" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" t="s">
+        <v>4</v>
+      </c>
+      <c r="L35" t="s">
+        <v>620</v>
+      </c>
+      <c r="M35" t="s">
+        <v>621</v>
+      </c>
+      <c r="N35" t="s">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>622</v>
+      </c>
+      <c r="P35" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>617</v>
+      </c>
+      <c r="B36" t="s">
+        <v>641</v>
+      </c>
+      <c r="C36" t="s">
+        <v>619</v>
+      </c>
+      <c r="D36">
+        <v>45625</v>
+      </c>
+      <c r="E36">
+        <v>23</v>
+      </c>
+      <c r="F36">
+        <v>23</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>4</v>
+      </c>
+      <c r="K36" t="s">
+        <v>4</v>
+      </c>
+      <c r="L36" t="s">
+        <v>620</v>
+      </c>
+      <c r="M36" t="s">
+        <v>621</v>
+      </c>
+      <c r="N36" t="s">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>622</v>
+      </c>
+      <c r="P36" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>3</v>
+      </c>
+      <c r="R36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>617</v>
+      </c>
+      <c r="B37" t="s">
+        <v>642</v>
+      </c>
+      <c r="C37" t="s">
+        <v>619</v>
+      </c>
+      <c r="D37">
+        <v>45625</v>
+      </c>
+      <c r="E37">
+        <v>23</v>
+      </c>
+      <c r="F37">
+        <v>23</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="J37" t="s">
+        <v>4</v>
+      </c>
+      <c r="K37" t="s">
+        <v>4</v>
+      </c>
+      <c r="L37" t="s">
+        <v>620</v>
+      </c>
+      <c r="M37" t="s">
+        <v>621</v>
+      </c>
+      <c r="N37" t="s">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>622</v>
+      </c>
+      <c r="P37" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>3</v>
+      </c>
+      <c r="R37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>617</v>
+      </c>
+      <c r="B38" t="s">
+        <v>643</v>
+      </c>
+      <c r="C38" t="s">
+        <v>619</v>
+      </c>
+      <c r="D38">
+        <v>45625</v>
+      </c>
+      <c r="E38">
+        <v>23</v>
+      </c>
+      <c r="F38">
+        <v>23</v>
+      </c>
+      <c r="G38">
+        <v>500</v>
+      </c>
+      <c r="J38" t="s">
+        <v>27</v>
+      </c>
+      <c r="K38" t="s">
+        <v>4</v>
+      </c>
+      <c r="L38" t="s">
+        <v>620</v>
+      </c>
+      <c r="M38" t="s">
+        <v>621</v>
+      </c>
+      <c r="N38" t="s">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>622</v>
+      </c>
+      <c r="P38" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>617</v>
+      </c>
+      <c r="B39" t="s">
+        <v>644</v>
+      </c>
+      <c r="C39" t="s">
+        <v>619</v>
+      </c>
+      <c r="D39">
+        <v>45625</v>
+      </c>
+      <c r="E39">
+        <v>23</v>
+      </c>
+      <c r="F39">
+        <v>23</v>
+      </c>
+      <c r="G39">
+        <v>1800</v>
+      </c>
+      <c r="I39" t="s">
+        <v>645</v>
+      </c>
+      <c r="J39" t="s">
+        <v>645</v>
+      </c>
+      <c r="K39" t="s">
+        <v>4</v>
+      </c>
+      <c r="L39" t="s">
+        <v>620</v>
+      </c>
+      <c r="M39" t="s">
+        <v>621</v>
+      </c>
+      <c r="N39" t="s">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>622</v>
+      </c>
+      <c r="P39" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>3</v>
+      </c>
+      <c r="R39" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4813409B-7228-2F49-BA7C-B95E948D09DC}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:O25"/>
@@ -7213,7 +9423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5EC7DD-B0EB-9B41-BA63-AAF43418DED7}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:O25"/>
@@ -8337,18 +10547,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3741EEE-A7B0-834D-9676-C4A7ABC54ECC}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:T344"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
@@ -9110,7 +11329,9 @@
       <c r="J26" s="16"/>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
-      <c r="M26" s="15"/>
+      <c r="M26" s="15" t="s">
+        <v>608</v>
+      </c>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
       <c r="P26" s="16"/>
@@ -9136,7 +11357,9 @@
       <c r="J27" s="16"/>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
-      <c r="M27" s="15"/>
+      <c r="M27" s="15" t="s">
+        <v>608</v>
+      </c>
       <c r="N27" s="16"/>
       <c r="O27" s="16"/>
       <c r="P27" s="16"/>
@@ -13580,7 +15803,9 @@
       <c r="L189" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="M189" s="15"/>
+      <c r="M189" s="15" t="s">
+        <v>609</v>
+      </c>
       <c r="N189" s="16"/>
       <c r="O189" s="16"/>
       <c r="P189" s="16"/>
@@ -13609,7 +15834,9 @@
       <c r="K190" s="16"/>
       <c r="L190" s="16"/>
       <c r="M190" s="16"/>
-      <c r="N190" s="15"/>
+      <c r="N190" s="15" t="s">
+        <v>611</v>
+      </c>
       <c r="O190" s="16"/>
       <c r="P190" s="16"/>
       <c r="Q190" s="16"/>
@@ -13634,7 +15861,9 @@
       <c r="J191" s="16"/>
       <c r="K191" s="16"/>
       <c r="L191" s="16"/>
-      <c r="M191" s="15"/>
+      <c r="M191" s="15" t="s">
+        <v>610</v>
+      </c>
       <c r="N191" s="16"/>
       <c r="O191" s="16"/>
       <c r="P191" s="16"/>
@@ -13664,8 +15893,12 @@
       <c r="L192" s="16"/>
       <c r="M192" s="16"/>
       <c r="N192" s="16"/>
-      <c r="O192" s="15"/>
-      <c r="P192" s="15"/>
+      <c r="O192" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="P192" s="15" t="s">
+        <v>613</v>
+      </c>
       <c r="Q192" s="16"/>
       <c r="R192" s="15"/>
       <c r="S192" s="15"/>
@@ -13719,7 +15952,9 @@
         <v>399</v>
       </c>
       <c r="M194" s="16"/>
-      <c r="N194" s="15"/>
+      <c r="N194" s="15" t="s">
+        <v>611</v>
+      </c>
       <c r="O194" s="16"/>
       <c r="P194" s="16"/>
       <c r="Q194" s="16"/>
@@ -13749,7 +15984,9 @@
         <v>399</v>
       </c>
       <c r="M195" s="16"/>
-      <c r="N195" s="15"/>
+      <c r="N195" s="15" t="s">
+        <v>611</v>
+      </c>
       <c r="O195" s="16"/>
       <c r="P195" s="16"/>
       <c r="Q195" s="16"/>
@@ -13779,7 +16016,9 @@
         <v>399</v>
       </c>
       <c r="M196" s="16"/>
-      <c r="N196" s="15"/>
+      <c r="N196" s="15" t="s">
+        <v>611</v>
+      </c>
       <c r="O196" s="16"/>
       <c r="P196" s="16"/>
       <c r="Q196" s="16"/>
@@ -13835,7 +16074,9 @@
         <v>399</v>
       </c>
       <c r="M198" s="16"/>
-      <c r="N198" s="15"/>
+      <c r="N198" s="15" t="s">
+        <v>611</v>
+      </c>
       <c r="O198" s="16"/>
       <c r="P198" s="16"/>
       <c r="Q198" s="16"/>
@@ -13970,11 +16211,17 @@
       <c r="L203" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="M203" s="15"/>
-      <c r="N203" s="15"/>
+      <c r="M203" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="N203" s="15" t="s">
+        <v>615</v>
+      </c>
       <c r="O203" s="16"/>
       <c r="P203" s="16"/>
-      <c r="Q203" s="15"/>
+      <c r="Q203" s="15" t="s">
+        <v>616</v>
+      </c>
       <c r="R203" s="15"/>
       <c r="S203" s="15"/>
       <c r="T203" s="15"/>
@@ -14022,7 +16269,9 @@
       <c r="J205" s="16"/>
       <c r="K205" s="16"/>
       <c r="L205" s="16"/>
-      <c r="M205" s="15"/>
+      <c r="M205" s="15" t="s">
+        <v>610</v>
+      </c>
       <c r="N205" s="16"/>
       <c r="O205" s="16"/>
       <c r="P205" s="16"/>
